--- a/feedback_surveys/024_customer_negative_feedback_handling_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/024_customer_negative_feedback_handling_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'chat',_'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Chat', 'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'escalate_to_manager',_'label':_'escalate_to_manager'}</t>
+          <t>escalate_to_manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Escalate to Manager', 'label': 'Escalate to Manager'}</t>
+          <t>Escalate to Manager</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'refund',_'label':_'refund'}</t>
+          <t>refund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Refund', 'label': 'Refund'}</t>
+          <t>Refund</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'replace_or_repair',_'label':_'replace_or_repair'}</t>
+          <t>replace_or_repair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Replace or Repair', 'label': 'Replace or Repair'}</t>
+          <t>Replace or Repair</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'not_done',_'label':_'not_done'}</t>
+          <t>not_done</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Not Done', 'label': 'Not Done'}</t>
+          <t>Not Done</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'done',_'label':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Done', 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'on_hold',_'label':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'On Hold', 'label': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'n/a',_'label':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'N/A', 'label': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'social_media',_'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media', 'label': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'in_app',_'label':_'in_app'}</t>
+          <t>in_app</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'In App', 'label': 'In App'}</t>
+          <t>In App</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'complaint',_'label':_'complaint'}</t>
+          <t>complaint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Complaint', 'label': 'Complaint'}</t>
+          <t>Complaint</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'suggestion',_'label':_'suggestion'}</t>
+          <t>suggestion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Suggestion', 'label': 'Suggestion'}</t>
+          <t>Suggestion</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'open',_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Open', 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'resolved',_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Resolved', 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'on_hold',_'label':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'On Hold', 'label': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'closed',_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Closed', 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
